--- a/配置表格/S属性配置表.xlsx
+++ b/配置表格/S属性配置表.xlsx
@@ -1747,7 +1747,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7.90833333333333" style="4" customWidth="1"/>
@@ -2463,8 +2463,10 @@
       <c r="F24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>82</v>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比</t>
+        </is>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -2494,8 +2496,10 @@
       <c r="F25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>82</v>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比</t>
+        </is>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -2525,8 +2529,10 @@
       <c r="F26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>82</v>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比</t>
+        </is>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -2556,8 +2562,10 @@
       <c r="F27" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>82</v>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比</t>
+        </is>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
@@ -2587,8 +2595,10 @@
       <c r="F28" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>82</v>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比</t>
+        </is>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -2618,8 +2628,10 @@
       <c r="F29" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>82</v>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比</t>
+        </is>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -2649,8 +2661,10 @@
       <c r="F30" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>82</v>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比</t>
+        </is>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -2680,8 +2694,10 @@
       <c r="F31" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>82</v>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比</t>
+        </is>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -2738,8 +2754,10 @@
       <c r="F33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>82</v>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比</t>
+        </is>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -2769,8 +2787,10 @@
       <c r="F34" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>82</v>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比</t>
+        </is>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -3222,14 +3242,18 @@
       <c r="F51" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G51" s="4" t="s">
-        <v>149</v>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">整数</t>
+        </is>
       </c>
       <c r="H51" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I51" s="4" t="s">
-        <v>149</v>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">整数</t>
+        </is>
       </c>
       <c r="J51" s="4" t="s">
         <v>150</v>
@@ -3252,14 +3276,18 @@
       <c r="F52" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G52" s="4" t="s">
-        <v>149</v>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">整数</t>
+        </is>
       </c>
       <c r="H52" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I52" s="4" t="s">
-        <v>149</v>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">整数</t>
+        </is>
       </c>
       <c r="J52" s="4" t="s">
         <v>152</v>
@@ -3282,8 +3310,10 @@
       <c r="F53" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G53" s="4" t="s">
-        <v>82</v>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比</t>
+        </is>
       </c>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
@@ -3307,8 +3337,10 @@
       <c r="F54" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="G54" s="4" t="s">
-        <v>82</v>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">万分比</t>
+        </is>
       </c>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
@@ -4219,6 +4251,166 @@
         <v>0</v>
       </c>
       <c r="N86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="4">
+        <v>83</v>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金行增幅</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金行神通造成的完整伤害提升x%（暴击与追加固定伤害之后整段相乘）</t>
+        </is>
+      </c>
+      <c r="N87" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="4">
+        <v>84</v>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">木行增幅</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">木行神通造成的完整伤害提升x%（暴击与追加固定伤害之后整段相乘）</t>
+        </is>
+      </c>
+      <c r="N88" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="4">
+        <v>85</v>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">水行增幅</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="3"/>
+      <c r="J89" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">水行神通造成的完整伤害提升x%（暴击与追加固定伤害之后整段相乘）</t>
+        </is>
+      </c>
+      <c r="N89" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="4">
+        <v>86</v>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火行增幅</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K90" s="4"/>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火行神通造成的完整伤害提升x%（暴击与追加固定伤害之后整段相乘）</t>
+        </is>
+      </c>
+      <c r="N90" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="4">
+        <v>87</v>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">土行增幅</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">土行神通造成的完整伤害提升x%（暴击与追加固定伤害之后整段相乘）</t>
+        </is>
+      </c>
+      <c r="N91" s="4" t="b">
         <v>1</v>
       </c>
     </row>
